--- a/results/notebooks/deterministic_route_ids.xlsx
+++ b/results/notebooks/deterministic_route_ids.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,11 +440,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/notebooks/deterministic_route_ids.xlsx
+++ b/results/notebooks/deterministic_route_ids.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/results/notebooks/deterministic_route_ids.xlsx
+++ b/results/notebooks/deterministic_route_ids.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,7 +437,447 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
